--- a/সমার্থক শব্দ.xlsx
+++ b/সমার্থক শব্দ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4CB7979-8C54-4D35-BE59-BBEF066E9D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD0346D6-8BAD-4B2B-9477-FD00BEF678B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{32A2C187-A571-464D-AD04-C63167D2AFB8}"/>
   </bookViews>
@@ -39,22 +39,162 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>সমার্থক শব্দ</t>
+  </si>
+  <si>
+    <t>স্বর্গ</t>
+  </si>
+  <si>
+    <t>অমরাবতী, দ্যুলোক, ত্রিদিব, দেবলোক, দিবালোক, সুরলোক, দ্যু, বেহেশত, সুরপুরী</t>
+  </si>
+  <si>
+    <t>শত্রু</t>
+  </si>
+  <si>
+    <t>প্রতিপক্ষ, বৈরী, অরাতি, রিপু, অরি</t>
+  </si>
+  <si>
+    <t>সাদা</t>
+  </si>
+  <si>
+    <t>সিত, সিতি, শুচি, শুক্ল, সফেদ, বলক্ষ</t>
+  </si>
+  <si>
+    <t>বধূ</t>
+  </si>
+  <si>
+    <t>কান্তা, জায়া, দার, কলত্র, বনিতা, দারা, ভার্যা, পত্নী, দয়িতা, অঙ্গনা, ধনিবা</t>
+  </si>
+  <si>
+    <t>কেশ</t>
+  </si>
+  <si>
+    <t>চুল, চিকুর, অলক, কবরী, কুন্তল, কেশপাশ, কেশদাম, চিকুর জাল</t>
+  </si>
+  <si>
+    <t>পৃথিবী</t>
+  </si>
+  <si>
+    <t>মেদিনী, ক্ষিতি, পৃথ্বী, অবনী, ধরণী, ধরা, বসুধা, উর্বী, ভূ-তল, মহী, রসা</t>
+  </si>
+  <si>
+    <t>পর্বত</t>
+  </si>
+  <si>
+    <t>মেদিনীধর, ক্ষিতিধর, পৃথ্বীধর, অবনীধর, ধরণীধর, ধরাধর, বসুধাধর, উর্বীধর, ভূধর, মহীধর, নগ, গিরি</t>
+  </si>
+  <si>
+    <t>রাজা</t>
+  </si>
+  <si>
+    <t>নৃপতি, ভূপ, ভূপাল, রাজ্যপাল, মহীন্দ্র, নরেশ, ক্ষিতিপতি, ক্ষিতিপ, ক্ষিতীশ, নৃপাল, নরপতি, নৃপ</t>
+  </si>
+  <si>
+    <t>নদী</t>
+  </si>
+  <si>
+    <t>তটিনী, প্রবাহিনী, গিরি নিঃস্রাব, কূলবতী, কলস্বিনী, গাঙ, নির্ঝরিণী, কল্লোলিনী, সরিৎ, স্রোতস্বতী, পয়স্বিনী, তরঙ্গিণী, শৈবালিনী, স্রোতস্বিনী, স্রোতঃস্বিনী, সমুদ্রকান্তা</t>
+  </si>
+  <si>
+    <t>পানি</t>
+  </si>
+  <si>
+    <t>জল, অম্বু, অপ, উদক, সলিল, বারি, নীর, তোয়, পয়, অম্বু, অর্ণ</t>
+  </si>
+  <si>
+    <t>সমুদ্র</t>
+  </si>
+  <si>
+    <t>জলধি, অম্বুধি, নীরধি, উদধি, বারিধি, তোয়ধি, তোয়নিধি, পয়োধি, পয়োনিধি, জলনিধি, অম্বুনিধি, বারিনিধি, বারীন্দ্র, পারাবার, রত্নাকর, সিন্ধু, অর্ণব, পাথার</t>
+  </si>
+  <si>
+    <t>মেঘ</t>
+  </si>
+  <si>
+    <t>অম্বুদ, অভ্র, ঘন, বলাহক, জীমূত, তোয়ধর, নীরদ, পর্জন্য, বারিদ, তোয়দ, পয়োদ, পয়োধর, জলদ, জলধর, কাদম্বিনী, অর্ণোদ</t>
+  </si>
+  <si>
+    <t>ঘোড়া</t>
+  </si>
+  <si>
+    <t>তুরগ, তুরঙ্গ, তুরঙ্গম, বড়বা, সপ্তি, রাজস্কন্ধা, বাজী, অশ্ব</t>
+  </si>
+  <si>
+    <t>ঢেউ</t>
+  </si>
+  <si>
+    <t>ঊর্মি, তরঙ্গ, চলোর্মি, লহর, লহরী, কল্লোল, হিল্লোল, বীচি, উল্লোল, মহোর্মী, দোলা</t>
+  </si>
+  <si>
+    <t>আগুন</t>
+  </si>
+  <si>
+    <t>অগ্নি, বহ্নি, পাবক, অনল, শিখা, কৃশানু, বিভাবসু, হুতাশন, বৈশ্বানর, দহন, সর্বভুক, সর্বশুচি, আশুগ, বায়ুসখা, বীতিহোত্র, হুতবহ</t>
+  </si>
+  <si>
+    <t>জ্যোৎস্না</t>
+  </si>
+  <si>
+    <t>কৌমুদী, পূর্ণেন্দু, শশিকর, চন্দ্রকর, চন্দ্রপ্রভা, চন্দ্রসুধা, চন্দ্রলোক, চন্দ্রিকা, চাঁদনী, দীপিকা, চন্দ্রাংশু</t>
+  </si>
+  <si>
+    <t>কিরণ</t>
+  </si>
+  <si>
+    <t>কর, প্রভা, দীপ্তি, অংশু, বিভা, ময়ূখ, উদ্ভাস, বসু, নূর, আভা, ভাতি</t>
+  </si>
+  <si>
+    <t>সূর্য</t>
+  </si>
+  <si>
+    <t>ভানু, তপন, রবি, মার্তণ্ড, সবিতা, মিহির, হরিদশ্ব, অর্ক, বালার্ক, দিনেশ, ময়ূখমালী, অংশুমালী, মিত্র, সূতপা, দিনপতি, সপ্তাশ্ব, গ্রহপতি, শূর, কিরণমালী, দিবানাথ, অহঃপতি</t>
+  </si>
+  <si>
+    <t>চাঁদ</t>
+  </si>
+  <si>
+    <t>চন্দ্র, বিধু, ইন্দু, শশী, শশাঙ্ক, শশধর, সুধাকর, সুধাংশু, সুধানিধি, সিতকর, হিমকর, নিশাকর, কলাধর, কলানিধি, কলাভৃৎ, সোম, হিমাংশু, রাকা, রাকেশ, রাকাপতি, মৃগাঙ্ক, সিতাংশু</t>
+  </si>
+  <si>
+    <t>বাতাস</t>
+  </si>
+  <si>
+    <t>সমীরণ, পবন, বাত, মরুৎ, অনিল</t>
+  </si>
+  <si>
+    <t>আনন্দ</t>
+  </si>
+  <si>
+    <t>হর্ষ, উল্লাস, উচ্ছ্বাস, আহ্লাদ, স্ফুর্তি, বিকাশ</t>
+  </si>
+  <si>
+    <t>শব্দ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Kalpurush"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Kalpurush"/>
     </font>
   </fonts>
   <fills count="2">
@@ -77,11 +217,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -416,19 +555,190 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C086CB59-C63C-4824-9A34-25244F35DC9C}">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="17.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="110.140625" style="2" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>42</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/সমার্থক শব্দ.xlsx
+++ b/সমার্থক শব্দ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD0346D6-8BAD-4B2B-9477-FD00BEF678B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2FAB79C-77DB-4543-B9C0-C913EDF40828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{32A2C187-A571-464D-AD04-C63167D2AFB8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{862D78E3-839A-4B44-9384-936A37931793}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,162 +39,403 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
-  <si>
-    <t>সমার্থক শব্দ</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
+  <si>
+    <t>মূল শব্দ</t>
+  </si>
+  <si>
+    <t>বিগত বছরের বিভিন্ন পরীক্ষায় আসা সমার্থক শব্দ</t>
+  </si>
+  <si>
+    <t>অন্যান্য প্রয়োজনীয় সমার্থক শব্দ</t>
+  </si>
+  <si>
+    <t>আলোক, কিরণ, অংশু, অংশুমালা, কর, দীপ্তি, প্রভা, রশ্মি, জ্যোতি, আভা, বিভা, ময়ূখ, দ্যুতি, ভাতি, রওশন।</t>
+  </si>
+  <si>
+    <t>ভাস, উদ্ভাস, চাকচিক্য, ঔজ্জ্বল্য, জেল্লা, জৌলুস, প্রদীপ্ত, নূর, বসু।</t>
+  </si>
+  <si>
+    <t>আদিত্য, আফতাব, মিহির, অরুণ, অর্ক, তপন, সৌর, সবিতা, ভানু, প্রভাকর, দিবাকর, বিভাকর, ভাস্কর, কিরণমালী, মার্তণ্ড, দিনেশ, দিনপতি, ময়ূখমালী, দিনকর, রবি, বালার্ক, অর্যমা।</t>
+  </si>
+  <si>
+    <t>দিনমণি, দিননাথ, উষাপতি, অংশুমালী, অংশুমান, পূষা, পূষণ, বিবস্বান, দিবাবসু, বিভাবসু, সূতপা, হরিদশ্ব।</t>
+  </si>
+  <si>
+    <t>চন্দ্র, সুধাকর, শশী, শশধর, শশাঙ্ক, দ্বিজরাজ, হিমাংশু, সুধাংশু, সোম, নিশাপতি, নিশাকর, নিশানথ, ইন্দু, বিধু, মৃগাঙ্ক, রাকেশ।</t>
+  </si>
+  <si>
+    <t>চন্দ্রমা, দ্বিজপতি, নিশাকান্ত, সিতাংশু, শীতাংশু, তারাপতি, তারানাথ, সুধানিধি, কলাধর, সিতকর, রজনীকান্ত, কলানিধি।</t>
+  </si>
+  <si>
+    <t>চন্দ্রিকা, চন্দ্রপ্রভা, চাঁদনি, কৌমুদী, শশিকর।</t>
+  </si>
+  <si>
+    <t>সুধা, চন্দ্রসুধা, চন্দ্রমা, চন্দ্রাংশু, চন্দ্রকর, চন্দ্রাতপ, চন্দ্রকিরণ।</t>
+  </si>
+  <si>
+    <t>অনল, বহ্নি, পাবক, কৃশানু, হুতাশন, বায়ুসখা, দহন, সর্বশুচি, সর্বভুক, অগ্নি, শিখা।</t>
+  </si>
+  <si>
+    <t>বৈশ্বানর, জগম্নু, হোমাগ্নি, জ্বলন, শিখিন, শিখবৎ, পিঙ্গল, বিশ্বপা, সপ্তাংশু, আতশ, পবমান, বীতিহোত্র।</t>
+  </si>
+  <si>
+    <t>বায়ু, বায়ূ, বাত, হাওয়া, পবন, গন্ধবহ, সমীর, সমীরণ, অনিল, প্রভঞ্জন, মരുത്, মারুত।</t>
+  </si>
+  <si>
+    <t>বা, শব্দবহ, আশুগ, পবমান, সদাগতি, অগ্নিসখ, বহ্নিসখ, জগতায়ু, মাতরিশ্বা।</t>
+  </si>
+  <si>
+    <t>কমল, উৎপল, পঙ্কজ, কুমুদ, অরবিন্দ, পুষ্কর, পুণ্ডরীক, রাজীব, শতদল, নলিন, নলিনী, সরোজ, সরসিজ, সরোরুহ, কোকনদ।</t>
+  </si>
+  <si>
+    <t>কুমুদী, কৈরব, কুবল, কুবলয়, অম্বোজ, কঞ্জ, তামরস, শ্রীপর্ণ, নীরজ, বিসজ, রাত্রিহাস, কুশেশয়, শশীকান্ত, ইন্দিরালয়।</t>
+  </si>
+  <si>
+    <t>গজ, নগজ, হস্তী, করী, দ্বিপ, বারণ, মাতঙ্গ, কুঞ্জর, দ্বিরদ, ইরম্মদ, ঐরাবত।</t>
+  </si>
+  <si>
+    <t>দন্তী, দন্তাবল, দ্রুমারি, ক্ষুদ্রাঙ্ক, করেণু, পিল, রদী, রদনী, কুনকি।</t>
+  </si>
+  <si>
+    <t>বিহগ, বিহঙ্গ, খগ, গরুড়, শকুন্ত, পক্ষী, পক্ষধর, খেচর।</t>
+  </si>
+  <si>
+    <t>বিহঙ্গম, খগম, অণ্ডজ, পতগ, পতশ্রী, পত্রী, পতত্রি, চিড়িয়া, দ্বিজ, পাখপাখালি।</t>
+  </si>
+  <si>
+    <t>অন্যপুষ্ট, পরপুষ্ট, কাকপুষ্ট, কলকণ্ঠ, পরভৃত, অন্যভৃত, পিক।</t>
+  </si>
+  <si>
+    <t>বসন্তদূত, মধুসখা, মধুস্বর, কুহুমন্দ্র, কোয়েলিয়া, কলঘোষ।</t>
+  </si>
+  <si>
+    <t>বায়স, পরভৃৎ।</t>
+  </si>
+  <si>
+    <t>কপোত, নোটন, লোটন, পায়রা, পারাবত।</t>
+  </si>
+  <si>
+    <t>কলাপী, কেকী, শিখী, শিখণ্ডী, বর্হী, বর্হিণ।</t>
+  </si>
+  <si>
+    <t>দ্রুম, পাদপ, উদ্ভিদ, অটবি, বিটপী।</t>
+  </si>
+  <si>
+    <t>তরু, শাখী, মহীরুহ, ক্ষিতিরুহ, পর্ণী, পত্রী, গাছপালা, পল্লবী।</t>
+  </si>
+  <si>
+    <t>নীর, অম্বু, অম্ভ, বারি, সলিল, উদ, উদক, প্রাণদ, তামর।</t>
+  </si>
+  <si>
+    <t>জল, বারুণ, পয়ঃ, তোয়, অপ, ইরা, ইলা, পুষ্কর, শম্বর।</t>
+  </si>
+  <si>
+    <t>বারিদ, অভ্র, জলদ, জলধর, পয়োদ, পয়োধর, নীরদ, নীরধর, তোয়দ, তোয়ধর, অম্বুদ, অম্বুধর, জীমূত, কাদম্বিনী, বলাহক।</t>
+  </si>
+  <si>
+    <t>বারিবাহ, বারিমুক, ঘন, অম্বুবাহ, অম্বুবাহী, পুষ্কর, মাহতাব।</t>
+  </si>
+  <si>
+    <t>সাগর, সিন্ধু, অর্ণব, দরিয়া, জলধি, জলনিধি, বারিধি, বারিনিধি, অম্বুধি, অম্বুনিধি, অম্বুরাশি, উদধি, পয়োধি, পয়োনিধি, পাথার, পারাবার, রত্নাকর, নীলাম্বু, মকরালয়, বারীন্দ্র, বারীশ, প্রচেতা।</t>
+  </si>
+  <si>
+    <t>সায়র, দ্বীপী, জলধর, বারিধর, তোয়ধি, তোয়নিধি, নীরধি, নীরনিধি, অকূল, জলারণ্য, নদীকান্ত, রত্নগর্ভ, ঊর্মিমালী, ইরাবান, হিরণ্যদ।</t>
+  </si>
+  <si>
+    <t>তরঙ্গ, ঊর্মি, মহোর্মী, চলোর্মি, চঞ্চলোর্মি, বীচি, লহরি, হিল্লোল, কল্লোল।</t>
+  </si>
+  <si>
+    <t>তরঙ্গমালা, তরঙ্গভঙ্গ, লহর, জলকল্লোল, দোলা, উল্লোল।</t>
+  </si>
+  <si>
+    <t>তটিনী, প্রবাহিনী, তরঙ্গিণী, নির্ঝরিণী, সরিৎ, শৈবলিনী, স্রোতস্বিনী, পয়স্বিনী, গাং।</t>
+  </si>
+  <si>
+    <t>কলস্বিনী, কল্লোলিনী, স্রোতোবহা, স্রোতস্বতী, সমুদ্রকান্তা, সমুদ্রদয়িতা, সমুদ্রবল্লভা।</t>
+  </si>
+  <si>
+    <t>সর্প, আশীবিষ, অহি, হরি, বায়ুভুক, ভুজঙ্গ, ফণী, উরগ, পন্নগ।</t>
+  </si>
+  <si>
+    <t>ভুজগ, ভুজঙ্গম, নাগ, কুণ্ডলিনী, বিষধর, দ্বিজিহ্ব, কাকোদর, ফণাধর।</t>
+  </si>
+  <si>
+    <t>কেশরী, মৃগেন্দ্র, হরি, হর্যক্ষ, পারীন্দ্র।</t>
+  </si>
+  <si>
+    <t>পশুরাজ, মৃগরাজ, মৃগপতি, সিংহিকা, দ্বিরদান্তক, কণ্ঠীরব।</t>
+  </si>
+  <si>
+    <t>বসুধা, বসুমতী, ধরিত্রী, ধরা, বসুন্ধরা, অচলা, ভূ, অদিতি, অখিল, ধরণি, অবনি, অবনিতল, মহি, মেদিনী, ক্ষিতি, পৃথ্বী, মর্ত্য, উর্বী।</t>
+  </si>
+  <si>
+    <t>ভুবন, ভূতল, ভূলোক, জ্যা, জগৎ, জাহান, ধরাতল, বসুমাতা, ভূমণ্ডল, মর্ত্যলোক, ব্রহ্মাণ্ড, ইরা, ইলা, সংসার, বিশ্ব, দুনিয়া।</t>
+  </si>
+  <si>
+    <t>অচল, গিরি, শৈল, পর্বত, অদ্রি, নগ, শৃঙ্গী, ভূধর, মহীধর, মেদিনীধর, শিখরী, জীমূত।</t>
+  </si>
+  <si>
+    <t>অগ, শৃঙ্গধর, ক্ষিতিধর, ক্ষিতিভৃৎ, ভূভৃৎ, অবনীধর, ধরণীধর, ধরাধর, পৃথ্বীধর।</t>
+  </si>
+  <si>
+    <t>ভূপতি, ভূপাল, মহীপতি, মহীপাল, মহীশ, নৃপ, নৃপতি, নৃপাল, নৃপেন্দ্র, নরেন্দ্র, ক্ষিতীশ, ক্ষিতিনাথ, পৃথ্বীশ, পৃথ্বীনাথ, অধিপতি, অধীশ, অধীশ্বর।</t>
+  </si>
+  <si>
+    <t>ভূপ, নৃপমণি, নরেশ, নরপতি, নরদেব, ক্ষিতীশ্বর, ক্ষিতিপতি, অধিপ, অধিরাজ, অধিভূ, প্রজানাথ, প্রজাপালক, জাহাপনা, বাদশা, পাতশা, সম্রাট, রাজেন্দ্র, রাজশেখর।</t>
+  </si>
+  <si>
+    <t>গগন, ব্যোম, অনন্ত, অম্বর, আসমান, খগোল, অন্তরীক্ষ, অভ্র, নীলিমা, শূন্য, নভ, নভঃ, খ।</t>
+  </si>
+  <si>
+    <t>বিমান, অম্বরতল, নভোমণ্ডল, ইথার, শূন্যলোক, নক্ষত্রলোক, নভোলোক, নভোমণ্ডল, দ্যৌ।</t>
+  </si>
+  <si>
+    <t>অশ্ব, বাজী, তুরগ, তুরঙ্গ, তুরঙ্গম, ঘোটক, হয়, বড়বা।</t>
+  </si>
+  <si>
+    <t>ঘোটকী, বাহ, হ্রেষী, সৈন্ধব, মরুদ্ৰথ, বামী, বাহনশ্রেষ্ঠ, টাঙ্গন।</t>
+  </si>
+  <si>
+    <t>মধুকর, মধুপ, অলি, ভৃঙ্গ, মৌমাছি, ষটপদ, শিলীমুখ, দ্বিরেফ।</t>
+  </si>
+  <si>
+    <t>মধুলিট, মধুলিহ, মধুলেহ, মধুলেহী, মধুব্রত, মধুমক্ষিকা, মধুভৃৎ, ভোমরা, বোলতা।</t>
+  </si>
+  <si>
+    <t>অরণ্য, কান্তার, বিপিন, অটবি, কানন, বনানী, বনশ্রী।</t>
+  </si>
+  <si>
+    <t>জঙ্গল, বনী, বনভূমি, বনাঞ্চল, বনরাজি, বাদাড়, অরণ্যানী, দাব, জঙ্গলাট।</t>
+  </si>
+  <si>
+    <t>তড়িৎ, ইরম্মদ, ক্ষণপ্রভা, দামিনী, সৌদামিনী, বিজলি, শম্পা।</t>
+  </si>
+  <si>
+    <t>চপলা, চঞ্চলা, বিজুরি, ক্ষণদ্যুতি, অশনি, অচির, অনুপ্রভা।</t>
+  </si>
+  <si>
+    <t>আঁধার, তিমির, অমানিশি, অমানিশা, তমিশ্রা।</t>
+  </si>
+  <si>
+    <t>তমিস্র, তমঃ, তমসা, শর্বর, অমা, নভাক, আলোকশূন্যতা।</t>
+  </si>
+  <si>
+    <t>রাত্রি, নিশি, নিশীথ, রজনি, যামিনী, অমানিশি, অমানিশা, শর্বরী, বিভাবরী, ক্ষণদা, শশিপ্রিয়া, ত্রিযামা।</t>
+  </si>
+  <si>
+    <t>নিশা, শমনী, যামী, যামিকা, যামবতী, নক্ত, নিশুতি, অসুরা, নিশীথিনী, ক্ষপা, তামসী, তারকিনী, অন্ধিকা, নিঃসম্পাত।</t>
+  </si>
+  <si>
+    <t>অমরা, অমরাবতী, দ্যুলোক, ঊর্ধ্বলোক, ত্রিদিব, বেহেশত।</t>
+  </si>
+  <si>
+    <t>দেবলোক, দেবপুরী, দেবালয়, ইন্দ্রলোক, অমর্ত্যলোক, ধ্রুবলোক, পুণ্যলোক, অমৃতলোক, ইন্দ্রপুরী।</t>
+  </si>
+  <si>
+    <t>আত্মজ, নন্দন, দুলাল, সুত, তনয়, তনুজ, দারক।</t>
+  </si>
+  <si>
+    <t>ছেলে, আত্মোদ্ভব, তনূদ্ভব, খোকা, স্বজ, কুমার, পুত্রক, পো, পুত, পুলে, পোলা, পোতক, বেটা, কোঙর।</t>
+  </si>
+  <si>
+    <t>আত্মজা, নন্দিনী, দুলালি, সুতা, দুহিতা, তনয়া।</t>
+  </si>
+  <si>
+    <t>মেয়ে, তনুজা, ঝি, পুত্রী, পুত্রিকা, দারিকা, কনে, বেটি, খুকি, কুমারী, পোতকী, ঝিয়ারি।</t>
+  </si>
+  <si>
+    <t>রামা, বামা, কান্তা, অবলা, মহিলা, ললনা, কামিনী, বনিতা, ভামিনী, সীমন্তিনী।</t>
+  </si>
+  <si>
+    <t>রমণী, অঙ্গনা, জনি, মেয়ে, মানবী, মানবিকা, বালা, জেনানা, যোষিৎ, প্রমদাজন, স্ত্রীলোক, যোষা।</t>
+  </si>
+  <si>
+    <t>ভার্যা, বনিতা, বধূ, জায়া, দার, পত্নী, অর্ধাঙ্গী, অঙ্গনা।</t>
+  </si>
+  <si>
+    <t>দয়িতা, আয়তি, এয়োতি, ধনিকা, গৃহিণী, গিন্নি, সহধর্মিণী, দারা, কলত্র, বল্লভা।</t>
+  </si>
+  <si>
+    <t>কবরী, চুল, কুন্তল, চিকুর, অলক।</t>
+  </si>
+  <si>
+    <t>কেশপাশ, কেশদাম, কচ, চিকুরজাল, শিরোজ, শিরসিজ।</t>
+  </si>
+  <si>
+    <t>কুসুম, পুষ্প, প্রসূন, মঞ্জরি, সুমন, অঙ্কুর, রঞ্জন।</t>
+  </si>
+  <si>
+    <t>চক্ষু, আঁখি, দর্শনেন্দ্রিয়, নয়ন, লোচন, নেত্র, অক্ষি, আঁখ।</t>
+  </si>
+  <si>
+    <t>ললাট, বরাত, অলিক, অদৃষ্ট।</t>
+  </si>
+  <si>
+    <t>ভাল, ভাগ্য, নিয়তি, দৈব।</t>
+  </si>
+  <si>
+    <t>শ্বেত, শুভ্র, শুক্ল, প্রসিত, ধবল, সফেদ, নির্মল, শুচি, সিত, বিশদ, অরঞ্জিত।</t>
+  </si>
+  <si>
+    <t>সুবর্ণ, কাঞ্চন, কনক, হেম, হিরণ, হিরণ্য, দ্রবিণ, কর্বুর, মহাধাতু।</t>
+  </si>
+  <si>
+    <t>পুলক, আহ্লাদ, সন্তোষ, হর্ষ, পরিতোষ, প্রমোদ, উল্লাস, তুষ্টি।</t>
+  </si>
+  <si>
+    <t>আমোদ, সুখ, স্ফুর্তি, ফুর্তি, উৎফুল্লতা, প্রফুল্লতা, প্রসন্নতা, হাসি, খুশি, হৃষ্টতা, মজা, রগড়।</t>
+  </si>
+  <si>
+    <t>অভিলাষ, অভিপ্রায়, লালসা, কামনা, স্পৃহা, বাসনা, অভিরুচি, ঈপ্সা, সাধ, আগ্রহ, বাঞ্ছা, প্রবৃত্তি।</t>
+  </si>
+  <si>
+    <t>আকাঙ্ক্ষা, মতি, মনোরথ, এষণা, আশা, প্রার্থনা, চাওয়া, মনোবাঞ্ছা, মনস্কাম।</t>
+  </si>
+  <si>
+    <t>আলো</t>
+  </si>
+  <si>
+    <t>কোকিল</t>
+  </si>
+  <si>
+    <t>কাক</t>
+  </si>
+  <si>
+    <t>কবুতর</t>
+  </si>
+  <si>
+    <t>ময়ূর</t>
+  </si>
+  <si>
+    <t>বৃক্ষ</t>
+  </si>
+  <si>
+    <t>পানি</t>
+  </si>
+  <si>
+    <t>মেঘ</t>
+  </si>
+  <si>
+    <t>সমুদ্র</t>
+  </si>
+  <si>
+    <t>ঢেউ</t>
+  </si>
+  <si>
+    <t>নদী</t>
+  </si>
+  <si>
+    <t>সূর্য</t>
+  </si>
+  <si>
+    <t>সাপ</t>
+  </si>
+  <si>
+    <t>সিংহ</t>
+  </si>
+  <si>
+    <t>পৃথিবী</t>
+  </si>
+  <si>
+    <t>পাহাড়</t>
+  </si>
+  <si>
+    <t>রাজা</t>
+  </si>
+  <si>
+    <t>আকাশ</t>
+  </si>
+  <si>
+    <t>ঘোড়া</t>
+  </si>
+  <si>
+    <t>চাঁদ</t>
+  </si>
+  <si>
+    <t>ভ্রমর</t>
+  </si>
+  <si>
+    <t>বন</t>
+  </si>
+  <si>
+    <t>বিদ্যুৎ</t>
+  </si>
+  <si>
+    <t>অন্ধকার</t>
+  </si>
+  <si>
+    <t>রাত</t>
   </si>
   <si>
     <t>স্বর্গ</t>
   </si>
   <si>
-    <t>অমরাবতী, দ্যুলোক, ত্রিদিব, দেবলোক, দিবালোক, সুরলোক, দ্যু, বেহেশত, সুরপুরী</t>
-  </si>
-  <si>
-    <t>শত্রু</t>
-  </si>
-  <si>
-    <t>প্রতিপক্ষ, বৈরী, অরাতি, রিপু, অরি</t>
+    <t>পুত্র</t>
+  </si>
+  <si>
+    <t>কন্যা</t>
+  </si>
+  <si>
+    <t>নারী</t>
+  </si>
+  <si>
+    <t>জ্যোৎস্না</t>
+  </si>
+  <si>
+    <t>স্ত্রী</t>
+  </si>
+  <si>
+    <t>কেশ</t>
+  </si>
+  <si>
+    <t>ফুল</t>
+  </si>
+  <si>
+    <t>চোখ</t>
+  </si>
+  <si>
+    <t>কপাল</t>
   </si>
   <si>
     <t>সাদা</t>
   </si>
   <si>
-    <t>সিত, সিতি, শুচি, শুক্ল, সফেদ, বলক্ষ</t>
-  </si>
-  <si>
-    <t>বধূ</t>
-  </si>
-  <si>
-    <t>কান্তা, জায়া, দার, কলত্র, বনিতা, দারা, ভার্যা, পত্নী, দয়িতা, অঙ্গনা, ধনিবা</t>
-  </si>
-  <si>
-    <t>কেশ</t>
-  </si>
-  <si>
-    <t>চুল, চিকুর, অলক, কবরী, কুন্তল, কেশপাশ, কেশদাম, চিকুর জাল</t>
-  </si>
-  <si>
-    <t>পৃথিবী</t>
-  </si>
-  <si>
-    <t>মেদিনী, ক্ষিতি, পৃথ্বী, অবনী, ধরণী, ধরা, বসুধা, উর্বী, ভূ-তল, মহী, রসা</t>
-  </si>
-  <si>
-    <t>পর্বত</t>
-  </si>
-  <si>
-    <t>মেদিনীধর, ক্ষিতিধর, পৃথ্বীধর, অবনীধর, ধরণীধর, ধরাধর, বসুধাধর, উর্বীধর, ভূধর, মহীধর, নগ, গিরি</t>
-  </si>
-  <si>
-    <t>রাজা</t>
-  </si>
-  <si>
-    <t>নৃপতি, ভূপ, ভূপাল, রাজ্যপাল, মহীন্দ্র, নরেশ, ক্ষিতিপতি, ক্ষিতিপ, ক্ষিতীশ, নৃপাল, নরপতি, নৃপ</t>
-  </si>
-  <si>
-    <t>নদী</t>
-  </si>
-  <si>
-    <t>তটিনী, প্রবাহিনী, গিরি নিঃস্রাব, কূলবতী, কলস্বিনী, গাঙ, নির্ঝরিণী, কল্লোলিনী, সরিৎ, স্রোতস্বতী, পয়স্বিনী, তরঙ্গিণী, শৈবালিনী, স্রোতস্বিনী, স্রোতঃস্বিনী, সমুদ্রকান্তা</t>
-  </si>
-  <si>
-    <t>পানি</t>
-  </si>
-  <si>
-    <t>জল, অম্বু, অপ, উদক, সলিল, বারি, নীর, তোয়, পয়, অম্বু, অর্ণ</t>
-  </si>
-  <si>
-    <t>সমুদ্র</t>
-  </si>
-  <si>
-    <t>জলধি, অম্বুধি, নীরধি, উদধি, বারিধি, তোয়ধি, তোয়নিধি, পয়োধি, পয়োনিধি, জলনিধি, অম্বুনিধি, বারিনিধি, বারীন্দ্র, পারাবার, রত্নাকর, সিন্ধু, অর্ণব, পাথার</t>
-  </si>
-  <si>
-    <t>মেঘ</t>
-  </si>
-  <si>
-    <t>অম্বুদ, অভ্র, ঘন, বলাহক, জীমূত, তোয়ধর, নীরদ, পর্জন্য, বারিদ, তোয়দ, পয়োদ, পয়োধর, জলদ, জলধর, কাদম্বিনী, অর্ণোদ</t>
-  </si>
-  <si>
-    <t>ঘোড়া</t>
-  </si>
-  <si>
-    <t>তুরগ, তুরঙ্গ, তুরঙ্গম, বড়বা, সপ্তি, রাজস্কন্ধা, বাজী, অশ্ব</t>
-  </si>
-  <si>
-    <t>ঢেউ</t>
-  </si>
-  <si>
-    <t>ঊর্মি, তরঙ্গ, চলোর্মি, লহর, লহরী, কল্লোল, হিল্লোল, বীচি, উল্লোল, মহোর্মী, দোলা</t>
+    <t>স্বর্ণ</t>
   </si>
   <si>
     <t>আগুন</t>
   </si>
   <si>
-    <t>অগ্নি, বহ্নি, পাবক, অনল, শিখা, কৃশানু, বিভাবসু, হুতাশন, বৈশ্বানর, দহন, সর্বভুক, সর্বশুচি, আশুগ, বায়ুসখা, বীতিহোত্র, হুতবহ</t>
-  </si>
-  <si>
-    <t>জ্যোৎস্না</t>
-  </si>
-  <si>
-    <t>কৌমুদী, পূর্ণেন্দু, শশিকর, চন্দ্রকর, চন্দ্রপ্রভা, চন্দ্রসুধা, চন্দ্রলোক, চন্দ্রিকা, চাঁদনী, দীপিকা, চন্দ্রাংশু</t>
-  </si>
-  <si>
-    <t>কিরণ</t>
-  </si>
-  <si>
-    <t>কর, প্রভা, দীপ্তি, অংশু, বিভা, ময়ূখ, উদ্ভাস, বসু, নূর, আভা, ভাতি</t>
-  </si>
-  <si>
-    <t>সূর্য</t>
-  </si>
-  <si>
-    <t>ভানু, তপন, রবি, মার্তণ্ড, সবিতা, মিহির, হরিদশ্ব, অর্ক, বালার্ক, দিনেশ, ময়ূখমালী, অংশুমালী, মিত্র, সূতপা, দিনপতি, সপ্তাশ্ব, গ্রহপতি, শূর, কিরণমালী, দিবানাথ, অহঃপতি</t>
-  </si>
-  <si>
-    <t>চাঁদ</t>
-  </si>
-  <si>
-    <t>চন্দ্র, বিধু, ইন্দু, শশী, শশাঙ্ক, শশধর, সুধাকর, সুধাংশু, সুধানিধি, সিতকর, হিমকর, নিশাকর, কলাধর, কলানিধি, কলাভৃৎ, সোম, হিমাংশু, রাকা, রাকেশ, রাকাপতি, মৃগাঙ্ক, সিতাংশু</t>
+    <t>আনন্দ</t>
+  </si>
+  <si>
+    <t>ইচ্ছা</t>
   </si>
   <si>
     <t>বাতাস</t>
   </si>
   <si>
-    <t>সমীরণ, পবন, বাত, মরুৎ, অনিল</t>
-  </si>
-  <si>
-    <t>আনন্দ</t>
-  </si>
-  <si>
-    <t>হর্ষ, উল্লাস, উচ্ছ্বাস, আহ্লাদ, স্ফুর্তি, বিকাশ</t>
-  </si>
-  <si>
-    <t>শব্দ</t>
+    <t>পদ্ম</t>
+  </si>
+  <si>
+    <t>হাতি</t>
+  </si>
+  <si>
+    <t>পাখি</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Kalpurush"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Kalpurush"/>
     </font>
   </fonts>
   <fills count="2">
@@ -217,10 +458,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -236,6 +475,21 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{850CE38F-F312-4AC1-BD42-880CAE3462C9}" name="Table3" displayName="Table3" ref="A1:C45" totalsRowShown="0">
+  <autoFilter ref="A1:C45" xr:uid="{850CE38F-F312-4AC1-BD42-880CAE3462C9}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C45">
+    <sortCondition ref="A1:A45"/>
+  </sortState>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{DD660FA3-E347-45BB-991C-BCCC86E5BDA2}" name="মূল শব্দ"/>
+    <tableColumn id="2" xr3:uid="{355C59F0-7E76-4702-97E9-9E32A869AEE4}" name="বিগত বছরের বিভিন্ন পরীক্ষায় আসা সমার্থক শব্দ"/>
+    <tableColumn id="3" xr3:uid="{2CD962CF-0969-410A-BCD9-5C9AA5E01883}" name="অন্যান্য প্রয়োজনীয় সমার্থক শব্দ"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -554,191 +808,493 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C086CB59-C63C-4824-9A34-25244F35DC9C}">
-  <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF32A57D-C54E-446E-9BA0-7BB37026E7E3}">
+  <dimension ref="A1:C45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="110.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="164" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="146.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A5" s="2" t="s">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C21" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" s="2" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>109</v>
+      </c>
+      <c r="B27" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>112</v>
+      </c>
+      <c r="B30" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C31" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" s="2" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>116</v>
+      </c>
+      <c r="B34" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>117</v>
+      </c>
+      <c r="B35" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>118</v>
+      </c>
+      <c r="B36" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>119</v>
+      </c>
+      <c r="B37" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>120</v>
+      </c>
+      <c r="B38" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>121</v>
+      </c>
+      <c r="B39" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C39" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A8" s="2" t="s">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>122</v>
+      </c>
+      <c r="B40" t="s">
+        <v>80</v>
+      </c>
+      <c r="C40" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>123</v>
+      </c>
+      <c r="B41" t="s">
+        <v>82</v>
+      </c>
+      <c r="C41" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>124</v>
+      </c>
+      <c r="B42" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C42" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" s="2" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>125</v>
+      </c>
+      <c r="B43" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C43" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A10" s="2" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>126</v>
+      </c>
+      <c r="B44" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C44" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A11" s="2" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>127</v>
+      </c>
+      <c r="B45" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C45" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A17" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A18" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A20" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A21" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A22" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>